--- a/data/trans_bre/IP1010-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,88</t>
+          <t>-2,03; 0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,79</t>
+          <t>-0,48; 3,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,49</t>
+          <t>-4,91; -0,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,01</t>
+          <t>-0,63; 1,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,0</t>
+          <t>-2,17; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -0,43</t>
+          <t>-3,68; -0,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-2,09; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -0,3</t>
+          <t>-2,56; -0,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,0</t>
+          <t>-2,01; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,01</t>
+          <t>-1,1; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,43</t>
+          <t>-0,51; 0,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; -0,2</t>
+          <t>-1,26; -0,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,02</t>
+          <t>-100,0; 55,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 501,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,95</t>
+          <t>-100,0; 21,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1010-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,88</t>
+          <t>-1,75; 0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,69</t>
+          <t>-0,55; 3,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,49</t>
+          <t>-4,95; -0,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,0</t>
+          <t>-0,63; 1,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-2,1; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,43</t>
+          <t>-3,72; -0,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,0</t>
+          <t>-2,03; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,3</t>
+          <t>-2,53; -0,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,0</t>
+          <t>-2,51; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,0</t>
+          <t>-1,1; 0,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,46</t>
+          <t>-0,54; 0,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; -0,19</t>
+          <t>-1,29; -0,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,49</t>
+          <t>-100,0; 50,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 501,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 21,55</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1010-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,88</t>
+          <t>-1,87; 0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,71</t>
+          <t>-0,48; 3,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -0,49</t>
+          <t>-4,88; -0,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; -0,43</t>
+          <t>-3,6; -0,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,0</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; -0,3</t>
+          <t>-2,49; -0,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,0</t>
+          <t>-2,23; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,22 +954,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,01</t>
+          <t>-1,09; 0,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,44</t>
+          <t>-0,54; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; -0,2</t>
+          <t>-1,34; -0,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,32</t>
+          <t>-100,0; 98,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 50,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1010-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,133 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-47,64%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>169,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.396965100018663</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7621134790552434</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.961791280635533</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.4764285239255395</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1.697637753906054</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 0,88</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,48; 3,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,88; -0,49</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.867013179909505</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.4843034135336741</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.876854341464557</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.8823283170274979</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.789120462939819</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.4912743783868778</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,63; 1,01</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,04; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.01432334482305269</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.5947328843553447</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.04554020547971017</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.6314442161636723</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>-2.039117111958468</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,6; -0,43</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,41</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,68</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.006107094420565</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,34 +737,26 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
+      <c r="C10" s="5" t="n">
+        <v>-1.346224710303273</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.2859933696610094</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3358168717247357</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -869,122 +764,192 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,89; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,49; -0,3</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,23; 0,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.604348513191941</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.428244785408788</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.408855841836559</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.677831714447915</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3370136669552471</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.9472997706350806</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3976240175779227</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.893374604159912</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.491657127096022</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.228605570045941</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.2985065428380335</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-71,59%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-16,32%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-89,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 0,01</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 0,43</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; -0,2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 98,02</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 50,95</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.4613969695845626</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.05778234500217975</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.6046056499110769</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.715899505874914</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1631924495058678</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.8904629660665447</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.094213932724019</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.5371027662545904</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.336739166604411</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.01042736305718092</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4302282788952098</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.2048575777734146</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.98021943279671</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="n">
+        <v>0.5095100806207004</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +958,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
